--- a/public/templates/Customer_sample_template.xlsx
+++ b/public/templates/Customer_sample_template.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20490" windowHeight="7620"/>
+    <workbookView windowWidth="23040" windowHeight="9120"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="38">
   <si>
     <t>Customer Name</t>
   </si>
@@ -110,22 +110,10 @@
     <t>GSTIN No.</t>
   </si>
   <si>
-    <t>TDS Applicable</t>
-  </si>
-  <si>
-    <t>TDS WEF Date</t>
+    <t>TCS Applicable</t>
   </si>
   <si>
     <t>TDS Certificate No.</t>
-  </si>
-  <si>
-    <t>TDS Tax %</t>
-  </si>
-  <si>
-    <t>TDS Category</t>
-  </si>
-  <si>
-    <t>TDS Value Cap</t>
   </si>
   <si>
     <t>TAN No.</t>
@@ -842,7 +830,7 @@
     <cellStyle name="Percent" xfId="3" builtinId="5"/>
     <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
     <cellStyle name="Currency [0]" xfId="5" builtinId="7"/>
-    <cellStyle name="Hyperlink" xfId="6" builtinId="8"/>
+    <cellStyle name="Link" xfId="6" builtinId="8"/>
     <cellStyle name="Followed Hyperlink" xfId="7" builtinId="9"/>
     <cellStyle name="Note" xfId="8" builtinId="10"/>
     <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
@@ -1173,8 +1161,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AH10"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
+  <dimension ref="A1:AD10"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="18.1416666666667" style="2" customWidth="1"/>
     <col min="2" max="2" width="12.7083333333333" style="2" customWidth="1"/>
@@ -1192,14 +1180,13 @@
     <col min="26" max="26" width="11.2833333333333" style="2" customWidth="1"/>
     <col min="27" max="27" width="9.14166666666667" style="2"/>
     <col min="28" max="28" width="11.425" style="2" customWidth="1"/>
-    <col min="29" max="29" width="9.14166666666667" style="2"/>
-    <col min="30" max="30" width="14.1416666666667" style="2" customWidth="1"/>
-    <col min="31" max="34" width="10.8583333333333" style="2" customWidth="1"/>
-    <col min="35" max="16383" width="9.14166666666667" style="2"/>
-    <col min="16384" max="16384" width="9" style="2"/>
+    <col min="29" max="29" width="14.1416666666667" style="2" customWidth="1"/>
+    <col min="30" max="30" width="10.8583333333333" style="2" customWidth="1"/>
+    <col min="31" max="16379" width="9.14166666666667" style="2"/>
+    <col min="16380" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="29.25" customHeight="1" spans="1:34">
+    <row r="1" s="1" customFormat="1" ht="29.25" customHeight="1" spans="1:30">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1290,35 +1277,23 @@
       <c r="AD1" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="AE1" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="AF1" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="AG1" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="AH1" s="4" t="s">
-        <v>33</v>
-      </c>
     </row>
-    <row r="2" ht="99.75" spans="1:34">
+    <row r="2" ht="96.6" spans="1:30">
       <c r="A2" s="6"/>
       <c r="B2" s="6" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C2" s="6"/>
       <c r="D2" s="6"/>
       <c r="E2" s="6"/>
       <c r="F2" s="6" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="I2" s="6"/>
       <c r="J2" s="6"/>
@@ -1330,7 +1305,7 @@
       <c r="P2" s="6"/>
       <c r="Q2" s="6"/>
       <c r="R2" s="6" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="S2" s="6"/>
       <c r="T2" s="6"/>
@@ -1340,32 +1315,20 @@
       <c r="X2" s="6"/>
       <c r="Y2" s="6"/>
       <c r="Z2" s="6" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="AA2" s="6"/>
       <c r="AB2" s="6" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AC2" s="6" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="AD2" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="AE2" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="AF2" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="AG2" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="AH2" s="6" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
     </row>
-    <row r="3" spans="1:34">
+    <row r="3" spans="1:30">
       <c r="A3" s="7"/>
       <c r="B3" s="7"/>
       <c r="C3" s="7"/>
@@ -1396,12 +1359,8 @@
       <c r="AB3" s="7"/>
       <c r="AC3" s="7"/>
       <c r="AD3" s="7"/>
-      <c r="AE3" s="7"/>
-      <c r="AF3" s="7"/>
-      <c r="AG3" s="7"/>
-      <c r="AH3" s="7"/>
     </row>
-    <row r="4" spans="1:34">
+    <row r="4" spans="1:30">
       <c r="A4" s="7"/>
       <c r="B4" s="7"/>
       <c r="C4" s="7"/>
@@ -1432,12 +1391,8 @@
       <c r="AB4" s="7"/>
       <c r="AC4" s="7"/>
       <c r="AD4" s="7"/>
-      <c r="AE4" s="7"/>
-      <c r="AF4" s="7"/>
-      <c r="AG4" s="7"/>
-      <c r="AH4" s="7"/>
     </row>
-    <row r="5" spans="1:34">
+    <row r="5" spans="1:30">
       <c r="A5" s="7"/>
       <c r="B5" s="7"/>
       <c r="C5" s="7"/>
@@ -1468,12 +1423,8 @@
       <c r="AB5" s="7"/>
       <c r="AC5" s="7"/>
       <c r="AD5" s="7"/>
-      <c r="AE5" s="7"/>
-      <c r="AF5" s="7"/>
-      <c r="AG5" s="7"/>
-      <c r="AH5" s="7"/>
     </row>
-    <row r="6" spans="1:34">
+    <row r="6" spans="1:30">
       <c r="A6" s="7"/>
       <c r="B6" s="7"/>
       <c r="C6" s="7"/>
@@ -1504,12 +1455,8 @@
       <c r="AB6" s="7"/>
       <c r="AC6" s="7"/>
       <c r="AD6" s="7"/>
-      <c r="AE6" s="7"/>
-      <c r="AF6" s="7"/>
-      <c r="AG6" s="7"/>
-      <c r="AH6" s="7"/>
     </row>
-    <row r="7" spans="1:34">
+    <row r="7" spans="1:30">
       <c r="A7" s="7"/>
       <c r="B7" s="7"/>
       <c r="C7" s="7"/>
@@ -1540,12 +1487,8 @@
       <c r="AB7" s="7"/>
       <c r="AC7" s="7"/>
       <c r="AD7" s="7"/>
-      <c r="AE7" s="7"/>
-      <c r="AF7" s="7"/>
-      <c r="AG7" s="7"/>
-      <c r="AH7" s="7"/>
     </row>
-    <row r="8" spans="1:34">
+    <row r="8" spans="1:30">
       <c r="A8" s="7"/>
       <c r="B8" s="7"/>
       <c r="C8" s="7"/>
@@ -1576,12 +1519,8 @@
       <c r="AB8" s="7"/>
       <c r="AC8" s="7"/>
       <c r="AD8" s="7"/>
-      <c r="AE8" s="7"/>
-      <c r="AF8" s="7"/>
-      <c r="AG8" s="7"/>
-      <c r="AH8" s="7"/>
     </row>
-    <row r="9" spans="1:34">
+    <row r="9" spans="1:30">
       <c r="A9" s="7"/>
       <c r="B9" s="7"/>
       <c r="C9" s="7"/>
@@ -1612,12 +1551,8 @@
       <c r="AB9" s="7"/>
       <c r="AC9" s="7"/>
       <c r="AD9" s="7"/>
-      <c r="AE9" s="7"/>
-      <c r="AF9" s="7"/>
-      <c r="AG9" s="7"/>
-      <c r="AH9" s="7"/>
     </row>
-    <row r="10" spans="1:34">
+    <row r="10" spans="1:30">
       <c r="A10" s="7"/>
       <c r="B10" s="7"/>
       <c r="C10" s="7"/>
@@ -1648,10 +1583,6 @@
       <c r="AB10" s="7"/>
       <c r="AC10" s="7"/>
       <c r="AD10" s="7"/>
-      <c r="AE10" s="7"/>
-      <c r="AF10" s="7"/>
-      <c r="AG10" s="7"/>
-      <c r="AH10" s="7"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/public/templates/Customer_sample_template.xlsx
+++ b/public/templates/Customer_sample_template.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="43">
   <si>
     <t>Customer Name</t>
   </si>
@@ -117,6 +117,15 @@
   </si>
   <si>
     <t>TAN No.</t>
+  </si>
+  <si>
+    <t>MSME Registered</t>
+  </si>
+  <si>
+    <t>MSME No.</t>
+  </si>
+  <si>
+    <t>MSME Type</t>
   </si>
   <si>
     <t>Mandatory if manual code is being used</t>
@@ -145,6 +154,17 @@
   </si>
   <si>
     <t>Mandatory if TDS applicable</t>
+  </si>
+  <si>
+    <t>Y/N
+No if left blank</t>
+  </si>
+  <si>
+    <t>sm - Small
+me -Medium
+pr -Producer
+tr - Trader
+bo - Brand Owner</t>
   </si>
 </sst>
 </file>
@@ -157,7 +177,7 @@
     <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="179" formatCode="_ &quot;₹&quot;* #,##0_ ;_ &quot;₹&quot;* \-#,##0_ ;_ &quot;₹&quot;* &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -169,6 +189,12 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <name val="Aptos Narrow"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -318,7 +344,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="36">
+  <fills count="37">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -345,6 +371,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -530,7 +562,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -542,6 +574,19 @@
       <left style="thin">
         <color auto="1"/>
       </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
       <right style="thin">
         <color auto="1"/>
       </right>
@@ -669,55 +714,52 @@
     <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="9" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -732,74 +774,77 @@
     <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -819,7 +864,10 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1161,8 +1209,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AD10"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
+  <dimension ref="A1:AG2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="18.1416666666667" style="2" customWidth="1"/>
     <col min="2" max="2" width="12.7083333333333" style="2" customWidth="1"/>
@@ -1182,11 +1230,13 @@
     <col min="28" max="28" width="11.425" style="2" customWidth="1"/>
     <col min="29" max="29" width="14.1416666666667" style="2" customWidth="1"/>
     <col min="30" max="30" width="10.8583333333333" style="2" customWidth="1"/>
-    <col min="31" max="16379" width="9.14166666666667" style="2"/>
-    <col min="16380" max="16384" width="9" style="2"/>
+    <col min="31" max="32" width="9.14166666666667" style="2"/>
+    <col min="33" max="33" width="10.9" style="2" customWidth="1"/>
+    <col min="34" max="16380" width="9.14166666666667" style="2"/>
+    <col min="16381" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="29.25" customHeight="1" spans="1:30">
+    <row r="1" s="1" customFormat="1" ht="29.25" customHeight="1" spans="1:33">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1277,23 +1327,32 @@
       <c r="AD1" s="4" t="s">
         <v>29</v>
       </c>
+      <c r="AE1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="AF1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="AG1" s="1" t="s">
+        <v>32</v>
+      </c>
     </row>
-    <row r="2" ht="96.6" spans="1:30">
+    <row r="2" ht="96.6" spans="1:33">
       <c r="A2" s="6"/>
       <c r="B2" s="6" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C2" s="6"/>
       <c r="D2" s="6"/>
       <c r="E2" s="6"/>
       <c r="F2" s="6" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="I2" s="6"/>
       <c r="J2" s="6"/>
@@ -1305,7 +1364,7 @@
       <c r="P2" s="6"/>
       <c r="Q2" s="6"/>
       <c r="R2" s="6" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="S2" s="6"/>
       <c r="T2" s="6"/>
@@ -1315,274 +1374,25 @@
       <c r="X2" s="6"/>
       <c r="Y2" s="6"/>
       <c r="Z2" s="6" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="AA2" s="6"/>
       <c r="AB2" s="6" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="AC2" s="6" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="AD2" s="6" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="3" spans="1:30">
-      <c r="A3" s="7"/>
-      <c r="B3" s="7"/>
-      <c r="C3" s="7"/>
-      <c r="D3" s="7"/>
-      <c r="E3" s="7"/>
-      <c r="F3" s="7"/>
-      <c r="G3" s="7"/>
-      <c r="H3" s="7"/>
-      <c r="I3" s="7"/>
-      <c r="J3" s="7"/>
-      <c r="K3" s="7"/>
-      <c r="L3" s="7"/>
-      <c r="M3" s="7"/>
-      <c r="N3" s="7"/>
-      <c r="O3" s="7"/>
-      <c r="P3" s="7"/>
-      <c r="Q3" s="7"/>
-      <c r="R3" s="7"/>
-      <c r="S3" s="7"/>
-      <c r="T3" s="7"/>
-      <c r="U3" s="7"/>
-      <c r="V3" s="7"/>
-      <c r="W3" s="7"/>
-      <c r="X3" s="7"/>
-      <c r="Y3" s="7"/>
-      <c r="Z3" s="7"/>
-      <c r="AA3" s="7"/>
-      <c r="AB3" s="7"/>
-      <c r="AC3" s="7"/>
-      <c r="AD3" s="7"/>
-    </row>
-    <row r="4" spans="1:30">
-      <c r="A4" s="7"/>
-      <c r="B4" s="7"/>
-      <c r="C4" s="7"/>
-      <c r="D4" s="7"/>
-      <c r="E4" s="7"/>
-      <c r="F4" s="7"/>
-      <c r="G4" s="7"/>
-      <c r="H4" s="7"/>
-      <c r="I4" s="7"/>
-      <c r="J4" s="7"/>
-      <c r="K4" s="7"/>
-      <c r="L4" s="7"/>
-      <c r="M4" s="7"/>
-      <c r="N4" s="7"/>
-      <c r="O4" s="7"/>
-      <c r="P4" s="7"/>
-      <c r="Q4" s="7"/>
-      <c r="R4" s="7"/>
-      <c r="S4" s="7"/>
-      <c r="T4" s="7"/>
-      <c r="U4" s="7"/>
-      <c r="V4" s="7"/>
-      <c r="W4" s="7"/>
-      <c r="X4" s="7"/>
-      <c r="Y4" s="7"/>
-      <c r="Z4" s="7"/>
-      <c r="AA4" s="7"/>
-      <c r="AB4" s="7"/>
-      <c r="AC4" s="7"/>
-      <c r="AD4" s="7"/>
-    </row>
-    <row r="5" spans="1:30">
-      <c r="A5" s="7"/>
-      <c r="B5" s="7"/>
-      <c r="C5" s="7"/>
-      <c r="D5" s="7"/>
-      <c r="E5" s="7"/>
-      <c r="F5" s="7"/>
-      <c r="G5" s="7"/>
-      <c r="H5" s="7"/>
-      <c r="I5" s="7"/>
-      <c r="J5" s="7"/>
-      <c r="K5" s="7"/>
-      <c r="L5" s="7"/>
-      <c r="M5" s="7"/>
-      <c r="N5" s="7"/>
-      <c r="O5" s="7"/>
-      <c r="P5" s="7"/>
-      <c r="Q5" s="7"/>
-      <c r="R5" s="7"/>
-      <c r="S5" s="7"/>
-      <c r="T5" s="7"/>
-      <c r="U5" s="7"/>
-      <c r="V5" s="7"/>
-      <c r="W5" s="7"/>
-      <c r="X5" s="7"/>
-      <c r="Y5" s="7"/>
-      <c r="Z5" s="7"/>
-      <c r="AA5" s="7"/>
-      <c r="AB5" s="7"/>
-      <c r="AC5" s="7"/>
-      <c r="AD5" s="7"/>
-    </row>
-    <row r="6" spans="1:30">
-      <c r="A6" s="7"/>
-      <c r="B6" s="7"/>
-      <c r="C6" s="7"/>
-      <c r="D6" s="7"/>
-      <c r="E6" s="7"/>
-      <c r="F6" s="7"/>
-      <c r="G6" s="7"/>
-      <c r="H6" s="7"/>
-      <c r="I6" s="7"/>
-      <c r="J6" s="7"/>
-      <c r="K6" s="7"/>
-      <c r="L6" s="7"/>
-      <c r="M6" s="7"/>
-      <c r="N6" s="7"/>
-      <c r="O6" s="7"/>
-      <c r="P6" s="7"/>
-      <c r="Q6" s="7"/>
-      <c r="R6" s="7"/>
-      <c r="S6" s="7"/>
-      <c r="T6" s="7"/>
-      <c r="U6" s="7"/>
-      <c r="V6" s="7"/>
-      <c r="W6" s="7"/>
-      <c r="X6" s="7"/>
-      <c r="Y6" s="7"/>
-      <c r="Z6" s="7"/>
-      <c r="AA6" s="7"/>
-      <c r="AB6" s="7"/>
-      <c r="AC6" s="7"/>
-      <c r="AD6" s="7"/>
-    </row>
-    <row r="7" spans="1:30">
-      <c r="A7" s="7"/>
-      <c r="B7" s="7"/>
-      <c r="C7" s="7"/>
-      <c r="D7" s="7"/>
-      <c r="E7" s="7"/>
-      <c r="F7" s="7"/>
-      <c r="G7" s="7"/>
-      <c r="H7" s="7"/>
-      <c r="I7" s="7"/>
-      <c r="J7" s="7"/>
-      <c r="K7" s="7"/>
-      <c r="L7" s="7"/>
-      <c r="M7" s="7"/>
-      <c r="N7" s="7"/>
-      <c r="O7" s="7"/>
-      <c r="P7" s="7"/>
-      <c r="Q7" s="7"/>
-      <c r="R7" s="7"/>
-      <c r="S7" s="7"/>
-      <c r="T7" s="7"/>
-      <c r="U7" s="7"/>
-      <c r="V7" s="7"/>
-      <c r="W7" s="7"/>
-      <c r="X7" s="7"/>
-      <c r="Y7" s="7"/>
-      <c r="Z7" s="7"/>
-      <c r="AA7" s="7"/>
-      <c r="AB7" s="7"/>
-      <c r="AC7" s="7"/>
-      <c r="AD7" s="7"/>
-    </row>
-    <row r="8" spans="1:30">
-      <c r="A8" s="7"/>
-      <c r="B8" s="7"/>
-      <c r="C8" s="7"/>
-      <c r="D8" s="7"/>
-      <c r="E8" s="7"/>
-      <c r="F8" s="7"/>
-      <c r="G8" s="7"/>
-      <c r="H8" s="7"/>
-      <c r="I8" s="7"/>
-      <c r="J8" s="7"/>
-      <c r="K8" s="7"/>
-      <c r="L8" s="7"/>
-      <c r="M8" s="7"/>
-      <c r="N8" s="7"/>
-      <c r="O8" s="7"/>
-      <c r="P8" s="7"/>
-      <c r="Q8" s="7"/>
-      <c r="R8" s="7"/>
-      <c r="S8" s="7"/>
-      <c r="T8" s="7"/>
-      <c r="U8" s="7"/>
-      <c r="V8" s="7"/>
-      <c r="W8" s="7"/>
-      <c r="X8" s="7"/>
-      <c r="Y8" s="7"/>
-      <c r="Z8" s="7"/>
-      <c r="AA8" s="7"/>
-      <c r="AB8" s="7"/>
-      <c r="AC8" s="7"/>
-      <c r="AD8" s="7"/>
-    </row>
-    <row r="9" spans="1:30">
-      <c r="A9" s="7"/>
-      <c r="B9" s="7"/>
-      <c r="C9" s="7"/>
-      <c r="D9" s="7"/>
-      <c r="E9" s="7"/>
-      <c r="F9" s="7"/>
-      <c r="G9" s="7"/>
-      <c r="H9" s="7"/>
-      <c r="I9" s="7"/>
-      <c r="J9" s="7"/>
-      <c r="K9" s="7"/>
-      <c r="L9" s="7"/>
-      <c r="M9" s="7"/>
-      <c r="N9" s="7"/>
-      <c r="O9" s="7"/>
-      <c r="P9" s="7"/>
-      <c r="Q9" s="7"/>
-      <c r="R9" s="7"/>
-      <c r="S9" s="7"/>
-      <c r="T9" s="7"/>
-      <c r="U9" s="7"/>
-      <c r="V9" s="7"/>
-      <c r="W9" s="7"/>
-      <c r="X9" s="7"/>
-      <c r="Y9" s="7"/>
-      <c r="Z9" s="7"/>
-      <c r="AA9" s="7"/>
-      <c r="AB9" s="7"/>
-      <c r="AC9" s="7"/>
-      <c r="AD9" s="7"/>
-    </row>
-    <row r="10" spans="1:30">
-      <c r="A10" s="7"/>
-      <c r="B10" s="7"/>
-      <c r="C10" s="7"/>
-      <c r="D10" s="7"/>
-      <c r="E10" s="7"/>
-      <c r="F10" s="7"/>
-      <c r="G10" s="7"/>
-      <c r="H10" s="7"/>
-      <c r="I10" s="7"/>
-      <c r="J10" s="7"/>
-      <c r="K10" s="7"/>
-      <c r="L10" s="7"/>
-      <c r="M10" s="7"/>
-      <c r="N10" s="7"/>
-      <c r="O10" s="7"/>
-      <c r="P10" s="7"/>
-      <c r="Q10" s="7"/>
-      <c r="R10" s="7"/>
-      <c r="S10" s="7"/>
-      <c r="T10" s="7"/>
-      <c r="U10" s="7"/>
-      <c r="V10" s="7"/>
-      <c r="W10" s="7"/>
-      <c r="X10" s="7"/>
-      <c r="Y10" s="7"/>
-      <c r="Z10" s="7"/>
-      <c r="AA10" s="7"/>
-      <c r="AB10" s="7"/>
-      <c r="AC10" s="7"/>
-      <c r="AD10" s="7"/>
+        <v>40</v>
+      </c>
+      <c r="AE2" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="AF2" s="8"/>
+      <c r="AG2" s="8" t="s">
+        <v>42</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
